--- a/samples/ss_kediri34_ingest.xlsx
+++ b/samples/ss_kediri34_ingest.xlsx
@@ -631,31 +631,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -702,15 +692,11 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -726,7 +712,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -773,15 +758,11 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -797,7 +778,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -826,31 +806,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -879,31 +849,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -932,31 +892,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -985,31 +935,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1038,19 +978,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1066,7 +998,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1095,31 +1026,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1148,19 +1069,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1176,7 +1089,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1205,19 +1117,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1233,7 +1137,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1262,19 +1165,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1290,7 +1185,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1319,19 +1213,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1347,7 +1233,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1376,17 +1261,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>batas ke UP2B Jateng (SS Pedan 3,4)</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -1402,13 +1281,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1437,19 +1314,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1465,7 +1334,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1494,31 +1362,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1547,31 +1405,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1600,31 +1448,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1671,19 +1509,16 @@
       <c r="J20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>IBT 150/70 kV; beban 73%</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1699,7 +1534,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1728,31 +1562,21 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1781,19 +1605,11 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1809,7 +1625,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1838,19 +1653,11 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1866,7 +1673,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1895,35 +1701,26 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>seksi A</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1952,31 +1749,21 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2023,15 +1810,11 @@
       <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2047,7 +1830,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2094,15 +1876,11 @@
       <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2118,7 +1896,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2147,31 +1924,21 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2200,35 +1967,26 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>seksi B</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2257,31 +2015,21 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2310,23 +2058,16 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>single busbar</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2342,7 +2083,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2389,15 +2129,11 @@
       <c r="J32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2413,7 +2149,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2460,15 +2195,11 @@
       <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2484,7 +2215,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2513,31 +2243,21 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2566,19 +2286,11 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2594,7 +2306,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2623,19 +2334,11 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2651,7 +2354,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2680,19 +2382,11 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2708,7 +2402,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2815,7 +2508,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Outlet PLTU Pacitan</t>
@@ -2836,7 +2528,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>1</v>
       </c>
@@ -2850,8 +2541,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2868,13 +2557,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Outlet PLTA Tlagong</t>
@@ -2895,7 +2582,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>1</v>
       </c>
@@ -2909,8 +2595,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2927,13 +2611,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>SUTT PLTU Pacitan - Ngadi</t>
@@ -2954,7 +2636,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>1</v>
       </c>
@@ -2968,8 +2649,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2986,7 +2665,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -3017,7 +2695,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>2</v>
       </c>
@@ -3031,8 +2708,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3049,13 +2724,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>SUTT Pacitan - Ponorogo</t>
@@ -3076,7 +2749,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -3090,8 +2762,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3108,7 +2778,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -3139,7 +2808,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>2</v>
       </c>
@@ -3153,8 +2821,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3171,7 +2837,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -3202,7 +2867,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -3216,8 +2880,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3234,7 +2896,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -3265,7 +2926,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>2</v>
       </c>
@@ -3279,8 +2939,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3297,7 +2955,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -3328,7 +2985,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -3342,8 +2998,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3360,13 +3014,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>SUTT Ngawi - Sragen (arah UP2B Jateng)</t>
@@ -3387,7 +3039,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>1</v>
       </c>
@@ -3401,8 +3052,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3419,7 +3068,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -3450,7 +3098,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>2</v>
       </c>
@@ -3464,8 +3111,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3482,13 +3127,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>SUTT Banaran - Mojoagung</t>
@@ -3509,7 +3152,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>2</v>
       </c>
@@ -3523,8 +3165,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3541,13 +3181,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>SUTT Banaran - Sukorejo</t>
@@ -3568,7 +3206,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>2</v>
       </c>
@@ -3582,8 +3219,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3600,13 +3235,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>SUTT Mojoagung - Kertosono</t>
@@ -3627,7 +3260,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>2</v>
       </c>
@@ -3641,8 +3273,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3659,13 +3289,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>SUTT Sukorejo - Kertosono</t>
@@ -3686,7 +3314,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>2</v>
       </c>
@@ -3700,8 +3327,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3718,7 +3343,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -3749,7 +3373,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>2</v>
       </c>
@@ -3763,8 +3386,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3781,7 +3402,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3812,7 +3432,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>2</v>
       </c>
@@ -3826,8 +3445,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3844,7 +3461,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3875,7 +3491,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>2</v>
       </c>
@@ -3889,8 +3504,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3907,13 +3520,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>SUTT 70 kV Tulungagung Pagerwojo - Tlagong A</t>
@@ -3934,7 +3545,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>2</v>
       </c>
@@ -3948,8 +3558,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3966,13 +3574,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>SUTT 70 kV Banaran - Tlagong B</t>
@@ -3993,7 +3599,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>2</v>
       </c>
@@ -4007,8 +3612,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4025,13 +3628,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>SUTT 70 kV Banaran - Gudang Garam</t>
@@ -4052,7 +3653,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>2</v>
       </c>
@@ -4066,8 +3666,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4084,7 +3682,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4115,7 +3712,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>2</v>
       </c>
@@ -4129,8 +3725,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4147,7 +3741,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4178,7 +3771,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>2</v>
       </c>
@@ -4192,8 +3784,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4210,7 +3800,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -4241,7 +3830,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>2</v>
       </c>
@@ -4255,8 +3843,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4273,7 +3859,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4342,7 +3927,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan IBT 500/150 kV 3 &amp; 4 GITET Kediri akan berbeban &gt;120% (realisasi Beban SS Kediri 3,4 = 945 MW) Ketika PLTU Pacitan outagesehinggatidak memenuhikriteriaN- 1</t>
+          <t>[N-1] Pembebanan IBT 500/150 kV 3 &amp; 4 GITET Kediri akan berbeban &gt;120% (realisasi Beban SS Kediri 3,4 = 945 MW) Ketika PLTU Pacitan outage sehingga tidak memenuhi kriteriaN- 1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4357,7 +3942,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>JangkaPendek: 1. Pembangunan PLTS 150 kV- 50 MW di Ngawi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2. Percepatan Pembangunan GITET 500 kV /Ngawi dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) informasi terupdate COD Desember 2027. Jangka Menengah : 3. Pembangunan PLTP Ngebel/PLTP Gunung Wilis dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). Jangka Panjang : 4. Pembangunan PLTP Gunung Lawu dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD diluar RUPTL). 5. Pembangunan PLTB 150 kV dengan Total 200 MW di Trenggalek (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033)</t>
+          <t>Jangka Pendek: 1. Pembangunan PLTS 150 kV - 50 MW di Ngawi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2. Percepatan Pembangunan GITET 500 kV /Ngawi dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) informasi terupdate COD Desember 2027. Jangka Menengah : 3. Pembangunan PLTP Ngebel/PLTP Gunung Wilis dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). Jangka Panjang : 4. Pembangunan PLTP Gunung Lawu dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD diluar RUPTL). 5. Pembangunan PLTB 150 kV dengan Total 200 MW di Trenggalek (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033)</t>
         </is>
       </c>
     </row>
@@ -4392,7 +3977,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Percepatan Pembangunan GITET 500 kV Madiun/Ngawi dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) informasi terupdate COD Desember 2027. 2. Usulan pemasangan Kapasitor sebesar GI New Pacitan (2x50 MVAR) COD Tahun 2026 (Surat UIP2B Jamali No. 2153/REN.00.01/F3300000 0/2024 tanggal 22 Mei 2024). JangkaPanjang: 3. Pembangunan SUTT 150 kV PLTU Pacitan - Trenggalek Baru. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2032). Usulan / Solusi 4. Pembangunan SUTT 150 kV Ponorogo - Trenggalek Baru. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2032). 5. Pembangunan SUTT 150 kV Trenggalek baru - Tx PLTA Tulungagung. (Berdasarkan RUPTL 2025 - 2034, COD diluar RUPTL). 6. Pembangunan SUTT 150 kV New Tulungagung-Tx PLTA Tulungagung. (Berdasarkan RUPTL 2025 - 2034, COD diluar RUPTL)</t>
+          <t>Jangka Pendek : 1. Percepatan Pembangunan GITET 500 kV Madiun/Ngawi dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) informasi terupdate COD Desember 2027. 2. Usulan pemasangan Kapasitor sebesar GI New Pacitan (2x50 MVAR) COD Tahun 2026 (Surat UIP2B Jamali No. 2153/REN.00.01/F3300000 0/2024 tanggal 22 Mei 2024). Jangka Panjang: 3. Pembangunan SUTT 150 kV PLTU Pacitan - Trenggalek Baru. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2032). Usulan / Solusi 4. Pembangunan SUTT 150 kV Ponorogo - Trenggalek Baru. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2032). 5. Pembangunan SUTT 150 kV Trenggalek baru - Tx PLTA Tulungagung. (Berdasarkan RUPTL 2025 - 2034, COD diluar RUPTL). 6. Pembangunan SUTT 150 kV New Tulungagung-Tx PLTA Tulungagung. (Berdasarkan RUPTL 2025 - 2034, COD diluar RUPTL)</t>
         </is>
       </c>
     </row>
@@ -4417,7 +4002,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1. TerjadiOverloadjika terjadi trip pada salah satu ruas tersebut. 2. Terjadi penurunan tegangan sebesar 5 kV saat ada pekerjaan ruas SUTT 150 kV Banaran- Surya tegangan di GI Suryazig-zag</t>
+          <t>1. Terjadi Overloadjika terjadi trip pada salah satu ruas tersebut. 2. Terjadi penurunan tegangan sebesar 5 kV saat ada pekerjaan ruas SUTT 150 kV Banaran- Surya tegangan di GI Surya zig-zag</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -4427,7 +4012,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>JangkaPendek: 1. Pembangunan PLTS 150 kV- 50 MW di Ngawi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2. Percepatan Pembangunan GITET 500 kV Madiun/Ngawi dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) informasi terupdate COD Desember 2027. 3. Normalisasi Doble phi SUTT 150 kV Banaran - Surya Zigzag - Nganjuk II. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). JangkaMenegah: 4. Pembangunan PLTP Wilis/Ngebel dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). Jangka Panjang : 5. Pembangunan PLTB 150 kV dengan Total 200 MW di Trenggalek (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033). 6. Pembangunan SUTT 150 kV PLTU Pacitan - Trenggalek Baru. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2032). 7. Pembangunan SUTT 150 kV Ponorogo - Trenggalek Baru. (Berdasarkan RUPTL Usulan / Solusi 2025 - 2034, COD Tahun 2032). 8. Pembangunan SUTT 150 kV Trenggalek baru - Tx PLTA Tulungagung. (Berdasarkan RUPTL 2025 - 2034, COD diluar RUPTL). 9. Pembangunan SUTT 150 kV New Tulungagung-Tx PLTA Tulungagung. (Berdasarkan RUPTL 2025 - 2034, COD diluar RUPTL). 10.Pembangunan PLTP Gunung Lawu dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD diluar periode RUPTL)</t>
+          <t>Jangka Pendek: 1. Pembangunan PLTS 150 kV - 50 MW di Ngawi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2. Percepatan Pembangunan GITET 500 kV Madiun/Ngawi dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) informasi terupdate COD Desember 2027. 3. Normalisasi Doble phi SUTT 150 kV Banaran - Surya Zigzag - Nganjuk II. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). Jangka Menegah: 4. Pembangunan PLTP Wilis/Ngebel dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). Jangka Panjang : 5. Pembangunan PLTB 150 kV dengan Total 200 MW di Trenggalek (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033). 6. Pembangunan SUTT 150 kV PLTU Pacitan - Trenggalek Baru. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2032). 7. Pembangunan SUTT 150 kV Ponorogo - Trenggalek Baru. (Berdasarkan RUPTL Usulan / Solusi 2025 - 2034, COD Tahun 2032). 8. Pembangunan SUTT 150 kV Trenggalek baru - Tx PLTA Tulungagung. (Berdasarkan RUPTL 2025 - 2034, COD diluar RUPTL). 9. Pembangunan SUTT 150 kV New Tulungagung-Tx PLTA Tulungagung. (Berdasarkan RUPTL 2025 - 2034, COD diluar RUPTL). 10. Pembangunan PLTP Gunung Lawu dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD diluar periode RUPTL)</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4047,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Usulan penambahan Busbar ke- 2 (Double Busbar) beserta Kopel Busbar di GI 150 kV Surya Zig- zag (diusulkan COD masuk di 2026)</t>
+          <t>Jangka Pendek : Usulan penambahan Busbar ke- 2 (Double Busbar) beserta Kopel Busbar di GI 150 kV Surya Zig- zag (diusulkan COD masuk di 2026)</t>
         </is>
       </c>
     </row>
@@ -4482,22 +4067,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[BELUM_DITETAPKAN] PHT150 kVBanaran- Surya zigzag-Nganjuk II - Manisrejoterjadi derating700 A dikarenakan ada penurunan andongan di ruas tersebut</t>
+          <t>[BELUM_DITETAPKAN] PHT 150 kV Banaran- Surya zigzag -Nganjuk II - Manisrejo terjadi derating 700 A dikarenakan ada penurunan andongan di ruas tersebut</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1. Kesulitan dalam melakukan pemeliharaan. 2. Jika PLTU Pacitantidak Operasi maka terjadiOverload di ruas tersebut</t>
+          <t>1. Kesulitan dalam melakukan pemeliharaan. 2. Jika PLTU Pacitan tidak Operasi maka terjadi Overload di ruas tersebut</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1. Penjadwalan pekerjaan dilakukan pada saatPLTU Pacitan Operasi. 2. SudahterpasangOLS eksistingSUTTBanara n-Surya Zigazag- Nganjuk IIdengantotal targetsebesar316M W(Berdasarkan Deklarasi ROB Mei 2026)</t>
+          <t>1. Penjadwalan pekerjaan dilakukan pada saat PLTU Pacitan Operasi. 2. Sudah terpasang OLS eksisting SUTTBanara n-Surya Zigazag- Nganjuk II dengan total target sebesar316M W (Berdasarkan Deklarasi ROB Mei 2026)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Pembangunan PLTS 150 kV- 50 MW di Ngawi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2. Percepatan Pembangunan GITET 500 kV Madiun/Ngawi dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) informasi terupdate COD Desember 2027. 3. Normalisasi Doble phi SUTT 150 kV Banaran - Surya Zigzag - Nganjuk II. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). Jangka Menegah : 4. Pembangunan PLTP Wilis/ Ngebel dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). Jangka Panjang : 5. Pembangunan PLTB 150 kV dengan Total 200 MW di Trenggalek (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033). Usulan / Solusi 6. Pembangunan SUTT 150 kV PLTU Pacitan - Trenggalek Baru. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2032). 7. Pembangunan SUTT 150 kV Ponorogo - Trenggalek Baru. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2032). 8. Pembangunan SUTT 150 kV Trenggalek baru - Tx PLTA Tulungagung. (Berdasarkan RUPTL 2025 - 2034, COD diluar RUPTL). 9. Pembangunan SUTT 150 kV New Tulungagung-Tx PLTA Tulungagung. (Berdasarkan RUPTL 2025 - 2034, COD diluar RUPTL). 10.Pembangunan PLTP Gunung Lawu dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD diluar periode RUPTL)</t>
+          <t>Jangka Pendek : 1. Pembangunan PLTS 150 kV - 50 MW di Ngawi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2. Percepatan Pembangunan GITET 500 kV Madiun/Ngawi dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) informasi terupdate COD Desember 2027. 3. Normalisasi Doble phi SUTT 150 kV Banaran - Surya Zigzag - Nganjuk II. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). Jangka Menegah : 4. Pembangunan PLTP Wilis/ Ngebel dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). Jangka Panjang : 5. Pembangunan PLTB 150 kV dengan Total 200 MW di Trenggalek (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033). Usulan / Solusi 6. Pembangunan SUTT 150 kV PLTU Pacitan - Trenggalek Baru. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2032). 7. Pembangunan SUTT 150 kV Ponorogo - Trenggalek Baru. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2032). 8. Pembangunan SUTT 150 kV Trenggalek baru - Tx PLTA Tulungagung. (Berdasarkan RUPTL 2025 - 2034, COD diluar RUPTL). 9. Pembangunan SUTT 150 kV New Tulungagung-Tx PLTA Tulungagung. (Berdasarkan RUPTL 2025 - 2034, COD diluar RUPTL). 10. Pembangunan PLTP Gunung Lawu dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD diluar periode RUPTL)</t>
         </is>
       </c>
     </row>
@@ -4532,7 +4117,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Extension IBT ke-2 150/70kV di GI Ponorogo. (Berdasarkan RUPTL 2025 - 2034, COD 2026. JangkaPanjang: 2. Pembangunan SUTT 150 kV PLTU Pacitan - Trenggalek Baru. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2032). 3. Percepatan pembangunan GI Trenggalek Baru 150 kV (- 2033. COD di 2032). 4. Pembangunan SUTT 150 kV Trenggalek baru - Tx PLTA Tulungagung. (Berdasarkan RUPTL 2025 - 2034, COD diluar RUPTL). 5. Pembangunan SUTT 150 kV New Tulungagung-Tx PLTA Tulungagung. (Berdasarkan RUPTL 2025 - 2034, COD diluar RUPTL)</t>
+          <t>Jangka Pendek : 1. Extension IBT ke-2 150/70kV di GI Ponorogo. (Berdasarkan RUPTL 2025 - 2034, COD 2026. Jangka Panjang: 2. Pembangunan SUTT 150 kV PLTU Pacitan - Trenggalek Baru. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2032). 3. Percepatan pembangunan GI Trenggalek Baru 150 kV (- 2033. COD di 2032). 4. Pembangunan SUTT 150 kV Trenggalek baru - Tx PLTA Tulungagung. (Berdasarkan RUPTL 2025 - 2034, COD diluar RUPTL). 5. Pembangunan SUTT 150 kV New Tulungagung-Tx PLTA Tulungagung. (Berdasarkan RUPTL 2025 - 2034, COD diluar RUPTL)</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4137,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[N-1] PembebananSUTT 70 kV Banaran- Tulungagung 1&amp;2 &gt;95% dansudahtidak memenuhikriteriaN- 1</t>
+          <t>[N-1] Pembebanan SUTT 70 kV Banaran- Tulungagung 1&amp;2 &gt;95% dan sudah tidak memenuhi kriteriaN- 1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4562,12 +4147,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1. Sudah terpasang OLS di SUTT Banaran- Tulungagung dengan total target sebesar63 Mitigasi MW. (Berdasarkan Deklarasi ROB Mei 2026). 2. Pekerjaan dilakukan saat beban rendah</t>
+          <t>1. Sudah terpasang OLS di SUTT Banaran- Tulungagung dengan total target sebesar 63 Mitigasi MW. (Berdasarkan Deklarasi ROB Mei 2026). 2. Pekerjaan dilakukan saat beban rendah</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Penambahan Trafo Distribusi 150/20 kV ke-2 kapasitas 60 MVA di GI 150 Usulan / Solusi kV New Tulungagung. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2. Penambahan Trafo Distribusi 150/20 kV ke-2 kapasitas 60 MVA di GI 150 kV New Wlingi. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 3. Penambahan Trafo Distribusi 150/20 kV ke-3 kapasitas 60 MVA di GI 150 kV New Tulungagung (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 4. Usulan agar Unit Distribusi membangun jaringan 20 kV baru agar beban 70kV di GI sekitar GI Tulungagung, GI PLTA Tulungagung, GI Blitar dan GI Wlingi bisa dialihkan ke GI 150 kV yang baru (GI New Tulungagung dan GI New Wlingi) (diusulkan COD masuk di 2026)</t>
+          <t>Jangka Pendek : 1. Penambahan Trafo Distribusi 150/20 kV ke-2 kapasitas 60 MVA di GI 150 Usulan / Solusi kV New Tulungagung. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2. Penambahan Trafo Distribusi 150/20 kV ke-2 kapasitas 60 MVA di GI 150 kV New Wlingi. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 3. Penambahan Trafo Distribusi 150/20 kV ke-3 kapasitas 60 MVA di GI 150 kV New Tulungagung (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 4. Usulan agar Unit Distribusi membangun jaringan 20 kV baru agar beban 70kV di GI sekitar GI Tulungagung, GI PLTA Tulungagung, GI Blitar dan GI Wlingi bisa dialihkan ke GI 150 kV yang baru (GI New Tulungagung dan GI New Wlingi) (diusulkan COD masuk di 2026)</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4172,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT 70 kVBanaran-Pare1&amp;2 beban &gt;80%dan tidak memenuhi kriteriaN- 1 dan konfigurasi masih radial</t>
+          <t>[N-1] Pembebanan SUTT 70 kV Banaran-Pare1&amp;2 beban &gt;80% dan tidak memenuhi kriteria N- 1 dan konfigurasi masih radial</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4602,7 +4187,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Usulan agar Unit Distribusi mengembangkan jaringan 20 kV di wilayah terkait sebelum GI Pare Baru II dan SUTT 150 kV Pare Baru II - Banaran beroperasi (diusulkan COD masuk di 2026). Jangka Panjang : 2. Pembangunan GI 150 kV Pare Baru dengan outlet memotong Banaran - Mojoagung (double phi). (Berdasarkan RUPTL 2025 - 2034, COD diluar periode RUPTL)</t>
+          <t>Jangka Pendek : 1. Usulan agar Unit Distribusi mengembangkan jaringan 20 kV di wilayah terkait sebelum GI Pare Baru II dan SUTT 150 kV Pare Baru II - Banaran beroperasi (diusulkan COD masuk di 2026). Jangka Panjang : 2. Pembangunan GI 150 kV Pare Baru dengan outlet memotong Banaran - Mojoagung (double phi). (Berdasarkan RUPTL 2025 - 2034, COD diluar periode RUPTL)</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4207,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[N-1] PembebananSUTT 70 kV Ponorogo- Trenggalek 1&amp;2 &gt;60% dan sudah tidak memenuhikriteriaN- 1</t>
+          <t>[N-1] Pembebanan SUTT 70 kV Ponorogo- Trenggalek 1&amp;2 &gt;60% dan sudah tidak memenuhi kriteriaN- 1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4632,7 +4217,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1. Sudah terpasang OLS di SUTT 70 kV Ponorogo-Trenggalek dengan total target sebesar 37 MW. (Berdasarkan Deklarasi ROB Mei 2026). 2. Pekerjaan dilakukan saat beban rendah</t>
+          <t>1. Sudah terpasang OLS di SUTT 70 kV Ponorogo -Trenggalek dengan total target sebesar 37 MW. (Berdasarkan Deklarasi ROB Mei 2026). 2. Pekerjaan dilakukan saat beban rendah</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4657,7 +4242,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[BELUM_DITETAPKAN] GI 70 kV Pare hanya singleBusbar</t>
+          <t>[BELUM_DITETAPKAN] GI 70 kV Pare hanya single Busbar</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4672,7 +4257,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>JangkaPendek: 1. Usulan penambahan Busbar ke-2 (Double Busbar) beserta Kopel Busbar di GI 70 kV Pare (Sesuai kajian operasi diusulkan COD di Tahun 2026). 2. Usulan agar Unit Distribusi mengembangkan jaringan 20 kV di wilayah terkait sebelum GI Pare Baru II dan SUTT 150 kV Pare Baru II - Banaran beroperasi (diusulkan COD masuk di 2026). Jangka Panjang : 3. Pembangunan GI 150 kV Pare Baru dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD di luar periode RUPTL). 4. Pembangunan SUTT 150 kV Pare Baru II - Incomer Banaran-Mojoagung (double phi). (Berdasarkan RUPTL 2025-2034, COD di luar periode RUPTL)</t>
+          <t>Jangka Pendek: 1. Usulan penambahan Busbar ke-2 (Double Busbar) beserta Kopel Busbar di GI 70 kV Pare (Sesuai kajian operasi diusulkan COD di Tahun 2026). 2. Usulan agar Unit Distribusi mengembangkan jaringan 20 kV di wilayah terkait sebelum GI Pare Baru II dan SUTT 150 kV Pare Baru II - Banaran beroperasi (diusulkan COD masuk di 2026). Jangka Panjang : 3. Pembangunan GI 150 kV Pare Baru dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD di luar periode RUPTL). 4. Pembangunan SUTT 150 kV Pare Baru II - Incomer Banaran-Mojoagung (double phi). (Berdasarkan RUPTL 2025 -2034, COD di luar periode RUPTL)</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4312,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[N-1-1] Kapasitas IBT 150/70 kV Manisrejo tidak sama (IBT-1: 100 MVA, IBT-2: 35 MVA, IBT-3: 100 MVA).Akan terjadi overload pada IBT 2 35 MVA apabila terjadi kontingensi N-1-1 pada IBT dengan kapasitas 100 MVA</t>
+          <t>[N-1-1] Kapasitas IBT 150/70 kV Manisrejo tidak sama (IBT-1: 100 MVA, IBT-2: 35 MVA, IBT-3: 100 MVA). Akan terjadi overload pada IBT 2 35 MVA apabila terjadi kontingensi N-1-1 pada IBT dengan kapasitas 100 MVA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -4762,7 +4347,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT 70 kV Manisrejo- Mranggen 1&amp;2 &gt;99% dan sudah tidak sesuai kriteriaN-1</t>
+          <t>[N-1] Pembebanan SUTT 70 kV Manisrejo- Mranggen 1&amp;2 &gt;99% dan sudah tidak sesuai kriteria N-1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -4797,7 +4382,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT 70 kV Mranggen- Magetan 1&amp;2 &gt;65% dan sudah tidak sesuai kriteriaN-1</t>
+          <t>[N-1] Pembebanan SUTT 70 kV Mranggen- Magetan 1&amp;2 &gt;65% dan sudah tidak sesuai kriteria N-1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -4847,7 +4432,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Jangka Pendek : 1. Usulan pemasangan Kapasitor sebesar 50 MVAR di GI New Nganjuk (2x25 MVAR) COD 2026 (Surat UIP2B Jamali No. 2153/REN.00.01/F3300000 0/2024 tanggal 22 Mei 2024). 2. Usulan pemasangan Kapasitor sebesar GI New Pacitan (2x50 MVAR) COD Tahun 2026 dan 20277(Surat UIP2B Jamali No. 2153/REN.00.01/F3300000 0/2024 tanggal 22 Mei 2024). 3. Usulan pemasangan Kapasitor di GI Wlingi II (50 MVAR)saat SUTT 150 kV New Wlingi - PLTA Wlingi Beroprasi, usulan COD Tahun 2027 (Sesuai Surat UIP2B Jamali No. 2153/REN.00.01/F3300000 0/2024 tanggal 22 Mei 2024)</t>
+          <t>Jangka Pendek : 1. Usulan pemasangan Kapasitor sebesar 50 MVAR di GI New Nganjuk (2x25 MVAR) COD 2026 (Surat UIP2B Jamali No. 2153/REN.00.01/F3300000 0/2024 tanggal 22 Mei 2024). 2. Usulan pemasangan Kapasitor sebesar GI New Pacitan (2x50 MVAR) COD Tahun 2026 dan 20277(Surat UIP2B Jamali No. 2153/REN.00.01/F3300000 0/2024 tanggal 22 Mei 2024). 3. Usulan pemasangan Kapasitor di GI Wlingi II (50 MVAR) saat SUTT 150 kV New Wlingi - PLTA Wlingi Beroprasi, usulan COD Tahun 2027 (Sesuai Surat UIP2B Jamali No. 2153/REN.00.01/F3300000 0/2024 tanggal 22 Mei 2024)</t>
         </is>
       </c>
     </row>
